--- a/Indomie Clients Details/Vip.xlsx
+++ b/Indomie Clients Details/Vip.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB2E226-4CF1-4C21-830B-B12A32E8C286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7F6AF4-41CA-4BE6-9A25-A0903518E3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3382,7 +3382,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -3410,7 +3410,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -4627,7 +4627,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -4655,7 +4655,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -5872,7 +5872,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -5900,7 +5900,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -7117,7 +7117,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -7145,7 +7145,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -8362,7 +8362,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -8390,7 +8390,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -9607,7 +9607,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -9635,7 +9635,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -10852,7 +10852,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -10880,7 +10880,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -12097,7 +12097,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -12125,7 +12125,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -13342,7 +13342,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -13370,7 +13370,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -14587,7 +14587,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -14615,7 +14615,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -18582,7 +18582,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -18610,7 +18610,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -19824,7 +19824,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -19852,7 +19852,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -21065,7 +21065,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -21093,7 +21093,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -22306,7 +22306,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -22334,7 +22334,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -23552,7 +23552,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -23580,7 +23580,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -25097,7 +25097,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -25125,7 +25125,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -26345,7 +26345,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -26373,7 +26373,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -27590,7 +27590,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -27618,7 +27618,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -28834,7 +28834,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -28862,7 +28862,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -30079,7 +30079,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -30107,7 +30107,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
@@ -31325,7 +31325,7 @@
       <c r="M4" s="203"/>
       <c r="N4" s="204">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="204"/>
       <c r="P4" s="204"/>
@@ -31353,7 +31353,7 @@
       <c r="M5" s="203"/>
       <c r="N5" s="204">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="202"/>
       <c r="P5" s="202"/>
